--- a/fixtures/xlsx/single_sheet_merge.xlsx
+++ b/fixtures/xlsx/single_sheet_merge.xlsx
@@ -35,7 +35,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:F1"/>
   </mergeCells>
 </worksheet>
 </file>